--- a/reports/tables/sensitivity_target_analysis_lightgbm_vs_catboost.xlsx
+++ b/reports/tables/sensitivity_target_analysis_lightgbm_vs_catboost.xlsx
@@ -493,28 +493,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3418471468871186</v>
+        <v>0.3426853340283033</v>
       </c>
       <c r="D2" t="n">
         <v>0.852112676056338</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3472348141432457</v>
+        <v>0.3522212148685404</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07751441383728379</v>
+        <v>0.07806451612903226</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9733163913595934</v>
+        <v>0.9736842105263158</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3351788756388416</v>
+        <v>0.3398637137989778</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6539383627239411</v>
+        <v>0.6568385836323472</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1470454912839782</v>
+        <v>0.1408160239635025</v>
       </c>
     </row>
     <row r="3">
@@ -527,28 +527,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4385547094523755</v>
+        <v>0.4445560901837345</v>
       </c>
       <c r="D3" t="n">
         <v>0.852112676056338</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3984587488667271</v>
+        <v>0.3970988213961922</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0835635359116022</v>
+        <v>0.0833907649896623</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9766666666666667</v>
+        <v>0.9765886287625418</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3833049403747871</v>
+        <v>0.3820272572402044</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6860993704748891</v>
+        <v>0.6837562090585215</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1414099501067443</v>
+        <v>0.1369107379895071</v>
       </c>
     </row>
     <row r="4">
@@ -561,28 +561,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.2402990708305414</v>
+        <v>0.233369531290189</v>
       </c>
       <c r="D4" t="n">
         <v>0.9014084507042254</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2048957388939256</v>
+        <v>0.185856754306437</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06801275239107332</v>
+        <v>0.06652806652806653</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9699570815450643</v>
+        <v>0.9669811320754716</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1984667802385008</v>
+        <v>0.1805792163543441</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6539383627239411</v>
+        <v>0.6568385836323472</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1470454912839782</v>
+        <v>0.1408160239635025</v>
       </c>
     </row>
     <row r="5">
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.3934197963705476</v>
+        <v>0.412803246533478</v>
       </c>
       <c r="D5" t="n">
         <v>0.9014084507042254</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2778785131459656</v>
+        <v>0.314143245693563</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07437536316095293</v>
+        <v>0.07800121876904327</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9776714513556619</v>
+        <v>0.9801980198019802</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2670357751277683</v>
+        <v>0.3011073253833049</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6860993704748891</v>
+        <v>0.6837562090585215</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1414099501067443</v>
+        <v>0.1369107379895071</v>
       </c>
     </row>
     <row r="6">
@@ -629,28 +629,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.1811043530161972</v>
+        <v>0.1866407274192785</v>
       </c>
       <c r="D6" t="n">
         <v>0.9507042253521126</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1060743427017226</v>
+        <v>0.1056210335448776</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06407214048410062</v>
+        <v>0.06404174573055028</v>
       </c>
       <c r="G6" t="n">
-        <v>0.970954356846473</v>
+        <v>0.9708333333333333</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1026405451448041</v>
+        <v>0.1022146507666099</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6539383627239411</v>
+        <v>0.6568385836323472</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1470454912839782</v>
+        <v>0.1408160239635025</v>
       </c>
     </row>
     <row r="7">
@@ -663,28 +663,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.3556449274794548</v>
+        <v>0.3363127545248334</v>
       </c>
       <c r="D7" t="n">
         <v>0.9507042253521126</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1504986400725295</v>
+        <v>0.128739800543971</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06719761075161772</v>
+        <v>0.06562955760816723</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9793510324483776</v>
+        <v>0.9759450171821306</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1443781942078365</v>
+        <v>0.1239352640545145</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6860993704748891</v>
+        <v>0.6837562090585215</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1414099501067443</v>
+        <v>0.1369107379895071</v>
       </c>
     </row>
   </sheetData>
@@ -751,13 +751,13 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0003580908162437636</v>
+        <v>0.0001408627063664623</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.01428828365878732</v>
+        <v>-0.01481481481481484</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01600322580645162</v>
+        <v>0.01600000000000001</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.05122393472348141</v>
+        <v>-0.04487760652765183</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.06554672419869982</v>
+        <v>-0.0574852916175525</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1536068648762359</v>
+        <v>-0.1730965132791268</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02256831423066552</v>
+        <v>0.02332095182054449</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -802,16 +802,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.006049122074318417</v>
+        <v>-0.005326248860630045</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.007919111353965121</v>
+        <v>-0.006292704471487381</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.01840563516791277</v>
+        <v>-0.01755440304016891</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002140906804014696</v>
+        <v>0.002877114878319249</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -829,16 +829,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.003350275307073325</v>
+        <v>-0.002904418236226003</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.00470947252213766</v>
+        <v>-0.004965778716998601</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01556167729250904</v>
+        <v>-0.02029379914496349</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001733756220597932</v>
+        <v>0.001693138053521085</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -856,16 +856,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.0481260647359455</v>
+        <v>-0.04216354344122658</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.06159364756877519</v>
+        <v>-0.05400503275414448</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1442041145240804</v>
+        <v>-0.1636468470606852</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02121069066253035</v>
+        <v>0.0216484423521308</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -886,13 +886,13 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000299607953533106</v>
+        <v>0.0004003678384335988</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0140845070422535</v>
+        <v>-0.01428571428571423</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01503759398496241</v>
+        <v>0.01527011156782151</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.07298277425203992</v>
+        <v>-0.128286491387126</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.06683902549728815</v>
+        <v>-0.09154899264580189</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1595380007741995</v>
+        <v>-0.1912594929097742</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02144704034780854</v>
+        <v>0.01137461815644353</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -937,16 +937,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.006362610769879609</v>
+        <v>-0.01147315224097674</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.006046782409115468</v>
+        <v>-0.008373856769909658</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.01510660957193662</v>
+        <v>-0.0185610634384195</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001869208697143662</v>
+        <v>0.0009573630338669013</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -964,16 +964,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.007714369810597588</v>
+        <v>-0.01321688772650853</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.007395938391030518</v>
+        <v>-0.009719124737738885</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.01996058466685173</v>
+        <v>-0.02231071000929235</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00130781306498506</v>
+        <v>0.001078637883675638</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -991,16 +991,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.06856899488926749</v>
+        <v>-0.1205281090289608</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.06279609796289892</v>
+        <v>-0.08601102792469982</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1496168797668883</v>
+        <v>-0.1797089451069681</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0202118662856227</v>
+        <v>0.01066823689932746</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1021,13 +1021,13 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.63696319300998e-05</v>
+        <v>0.0002416337549028145</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.01481481481481473</v>
+        <v>-0.01379310344827589</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01399097356544162</v>
+        <v>0.01460122370115927</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1045,16 +1045,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.0444242973708069</v>
+        <v>-0.02311876699909339</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.03996193615582458</v>
+        <v>-0.03675337325519495</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.114706541218638</v>
+        <v>-0.1540956570070531</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0311028529554866</v>
+        <v>0.01414149043976287</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1072,16 +1072,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.003125470267517097</v>
+        <v>-0.001587811877616946</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.00293291281971804</v>
+        <v>-0.002723066918772815</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.008776891269689965</v>
+        <v>-0.01297133707401097</v>
       </c>
       <c r="F14" t="n">
-        <v>0.002002268505795904</v>
+        <v>0.0006528581084320262</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1099,16 +1099,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.008396675601904602</v>
+        <v>-0.005111683848797233</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.008795032061403019</v>
+        <v>-0.007750566384348485</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.04379621018367828</v>
+        <v>-0.03302424510603565</v>
       </c>
       <c r="F15" t="n">
-        <v>0.008019010440728048</v>
+        <v>0.003700714887111079</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1126,16 +1126,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.04173764906303237</v>
+        <v>-0.0217206132879046</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.03754329353422884</v>
+        <v>-0.03454705552412939</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1074224666650113</v>
+        <v>-0.1441166705067614</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02944561977556604</v>
+        <v>0.01402900528378528</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1199,16 +1199,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3418471468871186</v>
+        <v>0.3426853340283033</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3343102554016796</v>
+        <v>0.3359380246101525</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2334899899925419</v>
+        <v>0.233369531290189</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4046547697409711</v>
+        <v>0.4206872156968289</v>
       </c>
     </row>
     <row r="3">
@@ -1221,16 +1221,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4385547094523755</v>
+        <v>0.4445560901837345</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4389577524030252</v>
+        <v>0.4422809082154415</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3870092707776027</v>
+        <v>0.4102622673607486</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4762872989119758</v>
+        <v>0.4671714260856066</v>
       </c>
     </row>
     <row r="4">
@@ -1243,16 +1243,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.2402990708305414</v>
+        <v>0.233369531290189</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2514692605032214</v>
+        <v>0.2455146874603953</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1871771881208519</v>
+        <v>0.1890118428792208</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3550559317177206</v>
+        <v>0.3657348152721732</v>
       </c>
     </row>
     <row r="5">
@@ -1265,16 +1265,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.3934197963705476</v>
+        <v>0.412803246533478</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3954371174119499</v>
+        <v>0.4039503420442563</v>
       </c>
       <c r="E5" t="n">
-        <v>0.355682957117221</v>
+        <v>0.3407895581998744</v>
       </c>
       <c r="F5" t="n">
-        <v>0.449639967649419</v>
+        <v>0.4460489195806071</v>
       </c>
     </row>
     <row r="6">
@@ -1287,16 +1287,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.1811043530161972</v>
+        <v>0.1866407274192785</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1798655831075769</v>
+        <v>0.1828265145286411</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1425560224546145</v>
+        <v>0.1491328523414462</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2334899899925419</v>
+        <v>0.2293505825317038</v>
       </c>
     </row>
     <row r="7">
@@ -1309,16 +1309,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.3556449274794548</v>
+        <v>0.3363127545248334</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3517974322450874</v>
+        <v>0.3404950169173782</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3214147776434966</v>
+        <v>0.3165059675243526</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3870092707776027</v>
+        <v>0.4102622673607486</v>
       </c>
     </row>
   </sheetData>
